--- a/config/tickers.xlsx
+++ b/config/tickers.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\EGX Project\egx-signals\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahmad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15330" windowHeight="5865"/>
   </bookViews>
   <sheets>
     <sheet name="Selected_Stocks" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="53">
   <si>
     <t>Ticker</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>ISMQ</t>
+  </si>
+  <si>
+    <t>ADCI</t>
+  </si>
+  <si>
+    <t>ICFC</t>
   </si>
 </sst>
 </file>
@@ -527,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -903,6 +909,22 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" t="s">
         <v>4</v>
       </c>
     </row>

--- a/config/tickers.xlsx
+++ b/config/tickers.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahmad\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="55">
   <si>
     <t>Ticker</t>
   </si>
@@ -180,6 +180,12 @@
   </si>
   <si>
     <t>ICFC</t>
+  </si>
+  <si>
+    <t>ORAS</t>
+  </si>
+  <si>
+    <t>MBEG</t>
   </si>
 </sst>
 </file>
@@ -533,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -926,6 +932,22 @@
       </c>
       <c r="B49" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
